--- a/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2020_los_lagos.xlsx
+++ b/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2020_los_lagos.xlsx
@@ -398,22 +398,22 @@
         </is>
       </c>
       <c r="B2">
+        <v>28.90593507694497</v>
+      </c>
+      <c r="C2">
         <v>20.42479785644844</v>
-      </c>
-      <c r="C2">
-        <v>28.90593507694497</v>
       </c>
       <c r="D2">
         <v>4.896009287476419</v>
       </c>
       <c r="E2">
-        <v>13.6775581658456</v>
+        <v>19.3569900241754</v>
       </c>
       <c r="F2">
         <v>66.965451809979</v>
       </c>
       <c r="G2">
-        <v>19.3569900241754</v>
+        <v>13.6775581658456</v>
       </c>
     </row>
     <row r="3">
@@ -423,22 +423,22 @@
         </is>
       </c>
       <c r="B3">
+        <v>28.60869956367235</v>
+      </c>
+      <c r="C3">
         <v>29.35990283837884</v>
-      </c>
-      <c r="C3">
-        <v>28.60869956367235</v>
       </c>
       <c r="D3">
         <v>3.406005821970277</v>
       </c>
       <c r="E3">
-        <v>18.58591035935987</v>
+        <v>18.11037075004272</v>
       </c>
       <c r="F3">
         <v>63.30371889059741</v>
       </c>
       <c r="G3">
-        <v>18.11037075004272</v>
+        <v>18.58591035935987</v>
       </c>
     </row>
     <row r="4">
@@ -448,22 +448,22 @@
         </is>
       </c>
       <c r="B4">
+        <v>27.43401125054089</v>
+      </c>
+      <c r="C4">
         <v>39.76633491994808</v>
-      </c>
-      <c r="C4">
-        <v>27.43401125054089</v>
       </c>
       <c r="D4">
         <v>2.514689880304679</v>
       </c>
       <c r="E4">
-        <v>23.78364389233955</v>
+        <v>16.40786749482402</v>
       </c>
       <c r="F4">
         <v>59.80848861283644</v>
       </c>
       <c r="G4">
-        <v>16.40786749482402</v>
+        <v>23.78364389233955</v>
       </c>
     </row>
     <row r="5">
@@ -473,22 +473,22 @@
         </is>
       </c>
       <c r="B5">
+        <v>27.47956403269755</v>
+      </c>
+      <c r="C5">
         <v>36.26702997275205</v>
-      </c>
-      <c r="C5">
-        <v>27.47956403269755</v>
       </c>
       <c r="D5">
         <v>2.75732531930879</v>
       </c>
       <c r="E5">
-        <v>22.14826524669274</v>
+        <v>16.78176220983443</v>
       </c>
       <c r="F5">
         <v>61.06997254347284</v>
       </c>
       <c r="G5">
-        <v>16.78176220983443</v>
+        <v>22.14826524669274</v>
       </c>
     </row>
     <row r="6">
@@ -498,22 +498,22 @@
         </is>
       </c>
       <c r="B6">
+        <v>29.16898166521153</v>
+      </c>
+      <c r="C6">
         <v>27.39899992062862</v>
-      </c>
-      <c r="C6">
-        <v>29.16898166521153</v>
       </c>
       <c r="D6">
         <v>3.649768250289687</v>
       </c>
       <c r="E6">
-        <v>17.49974652742573</v>
+        <v>18.63023420865862</v>
       </c>
       <c r="F6">
         <v>63.87001926391564</v>
       </c>
       <c r="G6">
-        <v>18.63023420865862</v>
+        <v>17.49974652742573</v>
       </c>
     </row>
     <row r="7">
@@ -523,22 +523,22 @@
         </is>
       </c>
       <c r="B7">
+        <v>29.44929812506135</v>
+      </c>
+      <c r="C7">
         <v>34.84833611465594</v>
-      </c>
-      <c r="C7">
-        <v>29.44929812506135</v>
       </c>
       <c r="D7">
         <v>2.869577464788732</v>
       </c>
       <c r="E7">
-        <v>21.21049172492084</v>
+        <v>17.92435920415845</v>
       </c>
       <c r="F7">
-        <v>60.86514907092072</v>
+        <v>60.86514907092071</v>
       </c>
       <c r="G7">
-        <v>17.92435920415845</v>
+        <v>21.21049172492083</v>
       </c>
     </row>
     <row r="8">
@@ -548,22 +548,22 @@
         </is>
       </c>
       <c r="B8">
+        <v>25.79537843268587</v>
+      </c>
+      <c r="C8">
         <v>27.99732083054253</v>
-      </c>
-      <c r="C8">
-        <v>25.79537843268587</v>
       </c>
       <c r="D8">
         <v>3.571770334928229</v>
       </c>
       <c r="E8">
-        <v>18.20458380967935</v>
+        <v>16.7728237791932</v>
       </c>
       <c r="F8">
         <v>65.02259241112745</v>
       </c>
       <c r="G8">
-        <v>16.7728237791932</v>
+        <v>18.20458380967935</v>
       </c>
     </row>
     <row r="9">
@@ -573,22 +573,22 @@
         </is>
       </c>
       <c r="B9">
+        <v>26.62119856887299</v>
+      </c>
+      <c r="C9">
         <v>37.26520572450805</v>
-      </c>
-      <c r="C9">
-        <v>26.62119856887299</v>
       </c>
       <c r="D9">
         <v>2.683468346834684</v>
       </c>
       <c r="E9">
-        <v>22.73843634875153</v>
+        <v>16.24368945285851</v>
       </c>
       <c r="F9">
-        <v>61.01787419838995</v>
+        <v>61.01787419838996</v>
       </c>
       <c r="G9">
-        <v>16.24368945285851</v>
+        <v>22.73843634875154</v>
       </c>
     </row>
     <row r="10">
@@ -598,22 +598,22 @@
         </is>
       </c>
       <c r="B10">
+        <v>28.17066570449215</v>
+      </c>
+      <c r="C10">
         <v>23.38986108605448</v>
-      </c>
-      <c r="C10">
-        <v>28.17066570449215</v>
       </c>
       <c r="D10">
         <v>4.275356729656768</v>
       </c>
       <c r="E10">
-        <v>15.43268658493037</v>
+        <v>18.58707296750387</v>
       </c>
       <c r="F10">
         <v>65.98024044756576</v>
       </c>
       <c r="G10">
-        <v>18.58707296750387</v>
+        <v>15.43268658493037</v>
       </c>
     </row>
     <row r="11">
@@ -623,22 +623,22 @@
         </is>
       </c>
       <c r="B11">
+        <v>25.53026461024432</v>
+      </c>
+      <c r="C11">
         <v>22.71113630261627</v>
-      </c>
-      <c r="C11">
-        <v>25.53026461024432</v>
       </c>
       <c r="D11">
         <v>4.40312623144621</v>
       </c>
       <c r="E11">
-        <v>15.32037350076471</v>
+        <v>17.22208806246478</v>
       </c>
       <c r="F11">
         <v>67.45753843677051</v>
       </c>
       <c r="G11">
-        <v>17.22208806246478</v>
+        <v>15.32037350076471</v>
       </c>
     </row>
     <row r="12">
@@ -648,22 +648,22 @@
         </is>
       </c>
       <c r="B12">
+        <v>25.82487080336815</v>
+      </c>
+      <c r="C12">
         <v>30.38560225506848</v>
-      </c>
-      <c r="C12">
-        <v>25.82487080336815</v>
       </c>
       <c r="D12">
         <v>3.291032350142721</v>
       </c>
       <c r="E12">
-        <v>19.45170618854829</v>
+        <v>16.5320994794679</v>
       </c>
       <c r="F12">
         <v>64.0161943319838</v>
       </c>
       <c r="G12">
-        <v>16.5320994794679</v>
+        <v>19.45170618854829</v>
       </c>
     </row>
     <row r="13">
@@ -673,22 +673,22 @@
         </is>
       </c>
       <c r="B13">
+        <v>27.26199420414297</v>
+      </c>
+      <c r="C13">
         <v>27.25126113555866</v>
-      </c>
-      <c r="C13">
-        <v>27.26199420414297</v>
       </c>
       <c r="D13">
         <v>3.669554942890902</v>
       </c>
       <c r="E13">
-        <v>17.63684356765768</v>
+        <v>17.64378994165046</v>
       </c>
       <c r="F13">
         <v>64.71936649069185</v>
       </c>
       <c r="G13">
-        <v>17.64378994165046</v>
+        <v>17.63684356765768</v>
       </c>
     </row>
     <row r="14">
@@ -698,22 +698,22 @@
         </is>
       </c>
       <c r="B14">
+        <v>30.23798413439104</v>
+      </c>
+      <c r="C14">
         <v>35.97760149323378</v>
-      </c>
-      <c r="C14">
-        <v>30.23798413439104</v>
       </c>
       <c r="D14">
         <v>2.779507133592737</v>
       </c>
       <c r="E14">
-        <v>21.64514317798989</v>
+        <v>18.19202695115104</v>
       </c>
       <c r="F14">
         <v>60.16282987085907</v>
       </c>
       <c r="G14">
-        <v>18.19202695115104</v>
+        <v>21.64514317798989</v>
       </c>
     </row>
     <row r="15">
@@ -723,22 +723,22 @@
         </is>
       </c>
       <c r="B15">
+        <v>29.42872397223705</v>
+      </c>
+      <c r="C15">
         <v>24.50613988254138</v>
-      </c>
-      <c r="C15">
-        <v>29.42872397223705</v>
       </c>
       <c r="D15">
         <v>4.080610021786493</v>
       </c>
       <c r="E15">
-        <v>15.91981132075471</v>
+        <v>19.11764705882353</v>
       </c>
       <c r="F15">
         <v>64.96254162042176</v>
       </c>
       <c r="G15">
-        <v>19.11764705882353</v>
+        <v>15.91981132075471</v>
       </c>
     </row>
     <row r="16">
@@ -748,22 +748,22 @@
         </is>
       </c>
       <c r="B16">
+        <v>26.52790079716563</v>
+      </c>
+      <c r="C16">
         <v>36.93534100974313</v>
-      </c>
-      <c r="C16">
-        <v>26.52790079716563</v>
       </c>
       <c r="D16">
         <v>2.707434052757794</v>
       </c>
       <c r="E16">
-        <v>22.59550257382823</v>
+        <v>16.22866431861284</v>
       </c>
       <c r="F16">
         <v>61.17583310755893</v>
       </c>
       <c r="G16">
-        <v>16.22866431861284</v>
+        <v>22.59550257382823</v>
       </c>
     </row>
     <row r="17">
@@ -773,22 +773,22 @@
         </is>
       </c>
       <c r="B17">
+        <v>27.53329473074696</v>
+      </c>
+      <c r="C17">
         <v>30.39953676896352</v>
-      </c>
-      <c r="C17">
-        <v>27.53329473074696</v>
       </c>
       <c r="D17">
         <v>3.28952380952381</v>
       </c>
       <c r="E17">
+        <v>17.43354720439963</v>
+      </c>
+      <c r="F17">
+        <v>63.31805682859761</v>
+      </c>
+      <c r="G17">
         <v>19.24839596700275</v>
-      </c>
-      <c r="F17">
-        <v>63.31805682859763</v>
-      </c>
-      <c r="G17">
-        <v>17.43354720439964</v>
       </c>
     </row>
     <row r="18">
@@ -798,22 +798,22 @@
         </is>
       </c>
       <c r="B18">
+        <v>30.51080238761819</v>
+      </c>
+      <c r="C18">
         <v>17.76451323226454</v>
-      </c>
-      <c r="C18">
-        <v>30.51080238761819</v>
       </c>
       <c r="D18">
         <v>5.629200118941421</v>
       </c>
       <c r="E18">
-        <v>11.98076237976488</v>
+        <v>20.57712860705379</v>
       </c>
       <c r="F18">
         <v>67.44210901318134</v>
       </c>
       <c r="G18">
-        <v>20.57712860705379</v>
+        <v>11.98076237976488</v>
       </c>
     </row>
     <row r="19">
@@ -823,22 +823,22 @@
         </is>
       </c>
       <c r="B19">
+        <v>27.58691206543967</v>
+      </c>
+      <c r="C19">
         <v>34.76482617586912</v>
-      </c>
-      <c r="C19">
-        <v>27.58691206543967</v>
       </c>
       <c r="D19">
         <v>2.876470588235294</v>
       </c>
       <c r="E19">
-        <v>21.41327623126338</v>
+        <v>16.99206449174959</v>
       </c>
       <c r="F19">
         <v>61.59465927698702</v>
       </c>
       <c r="G19">
-        <v>16.99206449174959</v>
+        <v>21.41327623126338</v>
       </c>
     </row>
     <row r="20">
@@ -848,22 +848,22 @@
         </is>
       </c>
       <c r="B20">
+        <v>26.95320770696591</v>
+      </c>
+      <c r="C20">
         <v>33.41096760533559</v>
-      </c>
-      <c r="C20">
-        <v>26.95320770696591</v>
       </c>
       <c r="D20">
         <v>2.993029150823828</v>
       </c>
       <c r="E20">
-        <v>20.83443358859255</v>
+        <v>16.80749933984684</v>
       </c>
       <c r="F20">
         <v>62.3580670715606</v>
       </c>
       <c r="G20">
-        <v>16.80749933984684</v>
+        <v>20.83443358859255</v>
       </c>
     </row>
     <row r="21">
@@ -873,22 +873,22 @@
         </is>
       </c>
       <c r="B21">
+        <v>26.58453749988618</v>
+      </c>
+      <c r="C21">
         <v>28.26172070620157</v>
-      </c>
-      <c r="C21">
-        <v>26.58453749988618</v>
       </c>
       <c r="D21">
         <v>3.538354972776185</v>
       </c>
       <c r="E21">
-        <v>18.25147151349794</v>
+        <v>17.16834349623375</v>
       </c>
       <c r="F21">
         <v>64.58018499026831</v>
       </c>
       <c r="G21">
-        <v>17.16834349623375</v>
+        <v>18.25147151349794</v>
       </c>
     </row>
     <row r="22">
@@ -898,22 +898,22 @@
         </is>
       </c>
       <c r="B22">
+        <v>29.27475856845295</v>
+      </c>
+      <c r="C22">
         <v>31.62279871236508</v>
-      </c>
-      <c r="C22">
-        <v>29.27475856845295</v>
       </c>
       <c r="D22">
         <v>3.162275449101796</v>
       </c>
       <c r="E22">
-        <v>19.65399552783335</v>
+        <v>18.19465693774274</v>
       </c>
       <c r="F22">
         <v>62.15134753442392</v>
       </c>
       <c r="G22">
-        <v>18.19465693774274</v>
+        <v>19.65399552783335</v>
       </c>
     </row>
     <row r="23">
@@ -923,22 +923,22 @@
         </is>
       </c>
       <c r="B23">
+        <v>27.36767149299786</v>
+      </c>
+      <c r="C23">
         <v>36.1658359047393</v>
-      </c>
-      <c r="C23">
-        <v>27.36767149299786</v>
       </c>
       <c r="D23">
         <v>2.765040472544301</v>
       </c>
       <c r="E23">
+        <v>16.73520731530311</v>
+      </c>
+      <c r="F23">
+        <v>61.14954763171901</v>
+      </c>
+      <c r="G23">
         <v>22.11524505297789</v>
-      </c>
-      <c r="F23">
-        <v>61.149547631719</v>
-      </c>
-      <c r="G23">
-        <v>16.73520731530311</v>
       </c>
     </row>
     <row r="24">
@@ -948,22 +948,22 @@
         </is>
       </c>
       <c r="B24">
+        <v>24.75208250694169</v>
+      </c>
+      <c r="C24">
         <v>34.06055797963771</v>
-      </c>
-      <c r="C24">
-        <v>24.75208250694169</v>
       </c>
       <c r="D24">
         <v>2.935947204968944</v>
       </c>
       <c r="E24">
-        <v>21.4470069103322</v>
+        <v>15.58571309632836</v>
       </c>
       <c r="F24">
         <v>62.96727999333944</v>
       </c>
       <c r="G24">
-        <v>15.58571309632836</v>
+        <v>21.4470069103322</v>
       </c>
     </row>
     <row r="25">
@@ -973,22 +973,22 @@
         </is>
       </c>
       <c r="B25">
+        <v>27.20008638375985</v>
+      </c>
+      <c r="C25">
         <v>36.65910808767951</v>
-      </c>
-      <c r="C25">
-        <v>27.20008638375985</v>
       </c>
       <c r="D25">
         <v>2.727835051546392</v>
       </c>
       <c r="E25">
-        <v>22.37232289950576</v>
+        <v>16.5996705107084</v>
       </c>
       <c r="F25">
         <v>61.02800658978583</v>
       </c>
       <c r="G25">
-        <v>16.5996705107084</v>
+        <v>22.37232289950576</v>
       </c>
     </row>
     <row r="26">
@@ -998,22 +998,22 @@
         </is>
       </c>
       <c r="B26">
+        <v>26.24854819976771</v>
+      </c>
+      <c r="C26">
         <v>43.5075493612079</v>
-      </c>
-      <c r="C26">
-        <v>26.24854819976771</v>
       </c>
       <c r="D26">
         <v>2.298451681793913</v>
       </c>
       <c r="E26">
-        <v>25.62944718117132</v>
+        <v>15.46250684181719</v>
       </c>
       <c r="F26">
         <v>58.9080459770115</v>
       </c>
       <c r="G26">
-        <v>15.46250684181719</v>
+        <v>25.62944718117132</v>
       </c>
     </row>
     <row r="27">
@@ -1023,22 +1023,22 @@
         </is>
       </c>
       <c r="B27">
+        <v>22.84180090871541</v>
+      </c>
+      <c r="C27">
         <v>37.75299463031805</v>
-      </c>
-      <c r="C27">
-        <v>22.84180090871541</v>
       </c>
       <c r="D27">
         <v>2.648796498905908</v>
       </c>
       <c r="E27">
-        <v>23.50823045267489</v>
+        <v>14.22325102880658</v>
       </c>
       <c r="F27">
         <v>62.26851851851851</v>
       </c>
       <c r="G27">
-        <v>14.22325102880658</v>
+        <v>23.50823045267489</v>
       </c>
     </row>
     <row r="28">
@@ -1048,22 +1048,22 @@
         </is>
       </c>
       <c r="B28">
+        <v>24.45488091244549</v>
+      </c>
+      <c r="C28">
         <v>29.3190204629319</v>
-      </c>
-      <c r="C28">
-        <v>24.45488091244549</v>
       </c>
       <c r="D28">
         <v>3.410755148741419</v>
       </c>
       <c r="E28">
+        <v>15.90314136125654</v>
+      </c>
+      <c r="F28">
+        <v>65.0305410122164</v>
+      </c>
+      <c r="G28">
         <v>19.06631762652705</v>
-      </c>
-      <c r="F28">
-        <v>65.03054101221642</v>
-      </c>
-      <c r="G28">
-        <v>15.90314136125655</v>
       </c>
     </row>
     <row r="29">
@@ -1073,22 +1073,22 @@
         </is>
       </c>
       <c r="B29">
+        <v>39.74096796182685</v>
+      </c>
+      <c r="C29">
         <v>32.719836400818</v>
-      </c>
-      <c r="C29">
-        <v>39.74096796182685</v>
       </c>
       <c r="D29">
         <v>3.05625</v>
       </c>
       <c r="E29">
-        <v>18.97233201581027</v>
+        <v>23.04347826086956</v>
       </c>
       <c r="F29">
         <v>57.98418972332016</v>
       </c>
       <c r="G29">
-        <v>23.04347826086956</v>
+        <v>18.97233201581027</v>
       </c>
     </row>
     <row r="30">
@@ -1098,22 +1098,22 @@
         </is>
       </c>
       <c r="B30">
+        <v>29.2565119889598</v>
+      </c>
+      <c r="C30">
         <v>25.89270312230464</v>
-      </c>
-      <c r="C30">
-        <v>29.2565119889598</v>
       </c>
       <c r="D30">
         <v>3.862091938707528</v>
       </c>
       <c r="E30">
-        <v>16.68890371358683</v>
+        <v>18.85701578830331</v>
       </c>
       <c r="F30">
-        <v>64.45408049810985</v>
+        <v>64.45408049810986</v>
       </c>
       <c r="G30">
-        <v>18.85701578830331</v>
+        <v>16.68890371358684</v>
       </c>
     </row>
     <row r="31">
@@ -1123,22 +1123,22 @@
         </is>
       </c>
       <c r="B31">
+        <v>27.20364741641338</v>
+      </c>
+      <c r="C31">
         <v>34.65045592705167</v>
-      </c>
-      <c r="C31">
-        <v>27.20364741641338</v>
       </c>
       <c r="D31">
         <v>2.885964912280702</v>
       </c>
       <c r="E31">
-        <v>21.40845070422535</v>
+        <v>16.8075117370892</v>
       </c>
       <c r="F31">
         <v>61.78403755868544</v>
       </c>
       <c r="G31">
-        <v>16.8075117370892</v>
+        <v>21.40845070422535</v>
       </c>
     </row>
   </sheetData>
